--- a/business_forms/043_tool_model_number_search_form--business_forms.xlsx
+++ b/business_forms/043_tool_model_number_search_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -836,7 +836,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Search Button2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tool Model Number</t>
+          <t>Tool Model Number2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tool Number</t>
+          <t>Tool Number2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -982,7 +982,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Search Results</t>
+          <t>Search Results2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>Supplier2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Store2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1126,8 +1126,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'supplier_a'}</t>
+          <t>supplier_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Supplier A'}</t>
+          <t>Supplier A</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'supplier_b'}</t>
+          <t>supplier_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Supplier B'}</t>
+          <t>Supplier B</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'store_a'}</t>
+          <t>store_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Store A'}</t>
+          <t>Store A</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'store_b'}</t>
+          <t>store_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Store B'}</t>
+          <t>Store B</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'store_c'}</t>
+          <t>store_c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Store C'}</t>
+          <t>Store C</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'search'}</t>
+          <t>search</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Search'}</t>
+          <t>Search</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'reset'}</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Reset'}</t>
+          <t>Reset</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'another_tool'}</t>
+          <t>another_tool</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'another_tool'}</t>
+          <t>another tool</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'search'}</t>
+          <t>search</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Search'}</t>
+          <t>Search</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'reset'}</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Reset'}</t>
+          <t>Reset</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'another_tool'}</t>
+          <t>another_tool</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'another_tool'}</t>
+          <t>another tool</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'supplier_a'}</t>
+          <t>supplier_a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Supplier A'}</t>
+          <t>Supplier A</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'supplier_b'}</t>
+          <t>supplier_b</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Supplier B'}</t>
+          <t>Supplier B</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'supplier_c'}</t>
+          <t>supplier_c</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Supplier C'}</t>
+          <t>Supplier C</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'store_a'}</t>
+          <t>store_a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Store A'}</t>
+          <t>Store A</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'store_b'}</t>
+          <t>store_b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Store B'}</t>
+          <t>Store B</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'store_c'}</t>
+          <t>store_c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Store C'}</t>
+          <t>Store C</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'store_d'}</t>
+          <t>store_d</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Store D'}</t>
+          <t>Store D</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'store_e'}</t>
+          <t>store_e</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Store E'}</t>
+          <t>Store E</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'store_f'}</t>
+          <t>store_f</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Store F'}</t>
+          <t>Store F</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'store_g'}</t>
+          <t>store_g</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Store G'}</t>
+          <t>Store G</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'store_h'}</t>
+          <t>store_h</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Store H'}</t>
+          <t>Store H</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'store_i'}</t>
+          <t>store_i</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Store I'}</t>
+          <t>Store I</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'store_j'}</t>
+          <t>store_j</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Store J'}</t>
+          <t>Store J</t>
         </is>
       </c>
     </row>
